--- a/booking_forms/009_ai_assistant_zoom_meeting_scheduling--booking_forms.xlsx
+++ b/booking_forms/009_ai_assistant_zoom_meeting_scheduling--booking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -923,8 +923,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
+    <col width="37" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -952,12 +952,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'initial_consultation',_'value':_'consultation'}</t>
+          <t>initial_consultation</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Initial Consultation', 'value': 'consultation'}</t>
+          <t>Initial Consultation</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'technical_support_/_troubleshooting',_'value':_'tech_support'}</t>
+          <t>technical_support_/_troubleshooting</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Technical Support / Troubleshooting', 'value': 'tech_support'}</t>
+          <t>Technical Support / Troubleshooting</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'product_demo',_'value':_'demo'}</t>
+          <t>product_demo</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Product Demo', 'value': 'demo'}</t>
+          <t>Product Demo</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'partnership_inquiry',_'value':_'partnership'}</t>
+          <t>partnership_inquiry</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Partnership Inquiry', 'value': 'partnership'}</t>
+          <t>Partnership Inquiry</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'follow-up_session',_'value':_'follow_up'}</t>
+          <t>follow-up_session</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Follow-up Session', 'value': 'follow_up'}</t>
+          <t>Follow-up Session</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'custom_llm_integration',_'value':_'custom_llm'}</t>
+          <t>custom_llm_integration</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Custom LLM Integration', 'value': 'custom_llm'}</t>
+          <t>Custom LLM Integration</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'openai_/_chatgpt_solutions',_'value':_'openai'}</t>
+          <t>openai_/_chatgpt_solutions</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'OpenAI / ChatGPT Solutions', 'value': 'openai'}</t>
+          <t>OpenAI / ChatGPT Solutions</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'anthropic_/_claude_integration',_'value':_'anthropic'}</t>
+          <t>anthropic_/_claude_integration</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Anthropic / Claude Integration', 'value': 'anthropic'}</t>
+          <t>Anthropic / Claude Integration</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'open-source_models_(llama,_etc.)',_'value':_'open_source'}</t>
+          <t>open-source_models_(llama,_etc.)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Open-Source Models (Llama, etc.)', 'value': 'open_source'}</t>
+          <t>Open-Source Models (Llama, etc.)</t>
         </is>
       </c>
     </row>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'customer_service_chatbots',_'value':_'customer_service'}</t>
+          <t>customer_service_chatbots</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Customer Service Chatbots', 'value': 'customer_service'}</t>
+          <t>Customer Service Chatbots</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'data_extraction_/_analysis',_'value':_'data_analysis'}</t>
+          <t>data_extraction_/_analysis</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Data Extraction / Analysis', 'value': 'data_analysis'}</t>
+          <t>Data Extraction / Analysis</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'morning_(9:00_am_-_12:00_pm)',_'value':_'morning'}</t>
+          <t>morning_(9:00_am_-_12:00_pm)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Morning (9:00 AM - 12:00 PM)', 'value': 'morning'}</t>
+          <t>Morning (9:00 AM - 12:00 PM)</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'afternoon_(12:00_pm_-_4:00_pm)',_'value':_'afternoon'}</t>
+          <t>afternoon_(12:00_pm_-_4:00_pm)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Afternoon (12:00 PM - 4:00 PM)', 'value': 'afternoon'}</t>
+          <t>Afternoon (12:00 PM - 4:00 PM)</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'evening_(4:00_pm_-_6:00_pm)',_'value':_'evening'}</t>
+          <t>evening_(4:00_pm_-_6:00_pm)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Evening (4:00 PM - 6:00 PM)', 'value': 'evening'}</t>
+          <t>Evening (4:00 PM - 6:00 PM)</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'utc-8_(pst)',_'value':_'pst'}</t>
+          <t>utc-8_(pst)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'UTC-8 (PST)', 'value': 'pst'}</t>
+          <t>UTC-8 (PST)</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'utc-5_(est)',_'value':_'est'}</t>
+          <t>utc-5_(est)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'UTC-5 (EST)', 'value': 'est'}</t>
+          <t>UTC-5 (EST)</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'utc+0_(gmt)',_'value':_'gmt'}</t>
+          <t>utc+0_(gmt)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'UTC+0 (GMT)', 'value': 'gmt'}</t>
+          <t>UTC+0 (GMT)</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'utc+1_(cet)',_'value':_'cet'}</t>
+          <t>utc+1_(cet)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'UTC+1 (CET)', 'value': 'cet'}</t>
+          <t>UTC+1 (CET)</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'utc+8_(sgt/hkt)',_'value':_'hkt'}</t>
+          <t>utc+8_(sgt/hkt)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'UTC+8 (SGT/HKT)', 'value': 'hkt'}</t>
+          <t>UTC+8 (SGT/HKT)</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'15_minutes_(quick_sync)',_'value':_'15_min'}</t>
+          <t>15_minutes_(quick_sync)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': '15 Minutes (Quick Sync)', 'value': '15_min'}</t>
+          <t>15 Minutes (Quick Sync)</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'30_minutes_(standard)',_'value':_'30_min'}</t>
+          <t>30_minutes_(standard)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': '30 Minutes (Standard)', 'value': '30_min'}</t>
+          <t>30 Minutes (Standard)</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'60_minutes_(deep_dive)',_'value':_'60_min'}</t>
+          <t>60_minutes_(deep_dive)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': '60 Minutes (Deep Dive)', 'value': '60_min'}</t>
+          <t>60 Minutes (Deep Dive)</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'yes,_currently_in_production',_'value':_'production'}</t>
+          <t>yes,_currently_in_production</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Yes, currently in production', 'value': 'production'}</t>
+          <t>Yes, currently in production</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'yes,_in_development/pilot',_'value':_'pilot'}</t>
+          <t>yes,_in_development/pilot</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Yes, in development/pilot', 'value': 'pilot'}</t>
+          <t>Yes, in development/pilot</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1360,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'no,_just_starting_out',_'value':_'none'}</t>
+          <t>no,_just_starting_out</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'No, just starting out', 'value': 'none'}</t>
+          <t>No, just starting out</t>
         </is>
       </c>
     </row>
